--- a/results/feature_selection/induction/wnp/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP_calc/metrics_global.xlsx
@@ -496,32 +496,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1, mu_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4206274317554217</v>
+        <v>0.9549162144816906</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08866469863502954</v>
+        <v>0.03034204200223189</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02569929235313235</v>
+        <v>0.002073944809055308</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1603099883136804</v>
+        <v>0.04554058419756282</v>
       </c>
       <c r="H2" t="n">
-        <v>678.7044775470335</v>
+        <v>204.60012545388</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1933012751205662</v>
+        <v>0.01647689702183153</v>
       </c>
       <c r="J2" t="n">
-        <v>-191.709758407312</v>
+        <v>-315.2717445807494</v>
       </c>
       <c r="K2" t="n">
-        <v>-185.7428062676191</v>
+        <v>-309.4180134250051</v>
       </c>
     </row>
     <row r="3">
@@ -531,36 +531,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4204302838144559</v>
+        <v>0.9522664359394886</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08864831448614442</v>
+        <v>0.03115562352336822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0257080372659042</v>
+        <v>0.002195839951390111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1603372610028754</v>
+        <v>0.04685979034727013</v>
       </c>
       <c r="H3" t="n">
-        <v>679.1003613972515</v>
+        <v>195.5243524485682</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1933665409417962</v>
+        <v>0.01685715718412651</v>
       </c>
       <c r="J3" t="n">
-        <v>-191.6913865020707</v>
+        <v>-314.3019132733184</v>
       </c>
       <c r="K3" t="n">
-        <v>-185.7244343623778</v>
+        <v>-310.3994258361556</v>
       </c>
     </row>
     <row r="4">
@@ -570,81 +570,81 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.4195931932130361</v>
+        <v>0.9515518307289221</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08857830252198971</v>
+        <v>0.03153168303988688</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02574516818523151</v>
+        <v>0.002228713228333022</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1604530092744649</v>
+        <v>0.04720924939387432</v>
       </c>
       <c r="H4" t="n">
-        <v>681.2772716509335</v>
+        <v>200.4684203320174</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1936436597657513</v>
+        <v>0.01709455004115648</v>
       </c>
       <c r="J4" t="n">
-        <v>-191.6134488896652</v>
+        <v>-313.5292061608155</v>
       </c>
       <c r="K4" t="n">
-        <v>-185.6464967499723</v>
+        <v>-309.6267187236526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.407282035347512</v>
+        <v>0.9480005860445961</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1171983856165254</v>
+        <v>0.0340522592432233</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02629125556066643</v>
+        <v>0.00239207762628829</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1621457848994738</v>
+        <v>0.04890887062985906</v>
       </c>
       <c r="H5" t="n">
-        <v>1909.301048759736</v>
+        <v>267.0767524443464</v>
       </c>
       <c r="I5" t="n">
-        <v>0.197719268288213</v>
+        <v>0.01827427852502296</v>
       </c>
       <c r="J5" t="n">
-        <v>-190.4800196967128</v>
+        <v>-309.8508355298504</v>
       </c>
       <c r="K5" t="n">
-        <v>-184.51306755702</v>
+        <v>-305.9483480926876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,71 +652,71 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3041721917020619</v>
+        <v>0.8954854271290891</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09217277521644285</v>
+        <v>0.03674135720070883</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03086491016837228</v>
+        <v>0.004807880558038522</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1756841204217737</v>
+        <v>0.06933888200741718</v>
       </c>
       <c r="H6" t="n">
-        <v>565.7309708409374</v>
+        <v>227.9981707321602</v>
       </c>
       <c r="I6" t="n">
-        <v>0.231353779607242</v>
+        <v>0.03571988825190025</v>
       </c>
       <c r="J6" t="n">
-        <v>-183.8193080149173</v>
+        <v>-273.549944068586</v>
       </c>
       <c r="K6" t="n">
-        <v>-179.8413399217887</v>
+        <v>-269.6474566314232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc</t>
+          <t>P, X_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2061500358374971</v>
+        <v>0.7898437461488077</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07852040843081151</v>
+        <v>0.0726232735043195</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0352128896529383</v>
+        <v>0.009667610356015505</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1876509782893186</v>
+        <v>0.09832400701769382</v>
       </c>
       <c r="H7" t="n">
-        <v>620.4368161334212</v>
+        <v>1426.95857491879</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2643040120058077</v>
+        <v>0.07081420340456855</v>
       </c>
       <c r="J7" t="n">
-        <v>-174.7025263245751</v>
+        <v>-237.2266542084102</v>
       </c>
       <c r="K7" t="n">
-        <v>-168.7355741848823</v>
+        <v>-233.3241667712473</v>
       </c>
     </row>
     <row r="8">
@@ -726,36 +726,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FS_calc, V_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05765168021544165</v>
+        <v>0.7417231589653051</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08839227782960241</v>
+        <v>0.0674211257034051</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04691437121366099</v>
+        <v>0.01188125414946732</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2165972557851576</v>
+        <v>0.1090011658170101</v>
       </c>
       <c r="H8" t="n">
-        <v>560.7889888737957</v>
+        <v>1097.617392671678</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7022711278283904</v>
+        <v>0.08629993021503563</v>
       </c>
       <c r="J8" t="n">
-        <v>-161.2092863120842</v>
+        <v>-228.5052569290943</v>
       </c>
       <c r="K8" t="n">
-        <v>-157.2313182189557</v>
+        <v>-226.5540132105128</v>
       </c>
     </row>
     <row r="9">
@@ -769,32 +769,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1035379068588524</v>
+        <v>0.7400454590884638</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09252063111947989</v>
+        <v>0.06631542598584311</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04894975158567974</v>
+        <v>0.01195843171809262</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2212459075004095</v>
+        <v>0.1093546145258289</v>
       </c>
       <c r="H9" t="n">
-        <v>631.5680497778034</v>
+        <v>931.8941862727604</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7316523963352632</v>
+        <v>0.08685726447612571</v>
       </c>
       <c r="J9" t="n">
-        <v>-160.9158931833541</v>
+        <v>-228.1685706479828</v>
       </c>
       <c r="K9" t="n">
-        <v>-158.9269091367898</v>
+        <v>-226.2173269294014</v>
       </c>
     </row>
     <row r="10">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.297141981220062</v>
+        <v>0.6880130474590302</v>
       </c>
       <c r="E10" t="n">
-        <v>0.141117108876108</v>
+        <v>0.08536575564125881</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05753746867908886</v>
+        <v>0.01435202730375318</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2398696910388823</v>
+        <v>0.1197999470106443</v>
       </c>
       <c r="H10" t="n">
-        <v>1717.666775641799</v>
+        <v>1494.477364990323</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8598376448827617</v>
+        <v>0.1041425048749182</v>
       </c>
       <c r="J10" t="n">
-        <v>-152.1872213665521</v>
+        <v>-218.6809317040683</v>
       </c>
       <c r="K10" t="n">
-        <v>-150.1982373199878</v>
+        <v>-216.7296879854869</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/induction/wnp/rP_calc/metrics_global.xlsx
+++ b/results/feature_selection/induction/wnp/rP_calc/metrics_global.xlsx
@@ -496,32 +496,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, Plag1, mu_calc</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9549162144816906</v>
+        <v>0.4122258894643192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03034204200223189</v>
+        <v>0.08995390518350994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002073944809055308</v>
+        <v>0.0270387912511808</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04554058419756282</v>
+        <v>0.1644347629036537</v>
       </c>
       <c r="H2" t="n">
-        <v>204.60012545388</v>
+        <v>676.5929596222103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01647689702183153</v>
+        <v>0.1967593870365308</v>
       </c>
       <c r="J2" t="n">
-        <v>-315.2717445807494</v>
+        <v>-181.7451020149005</v>
       </c>
       <c r="K2" t="n">
-        <v>-309.4180134250051</v>
+        <v>-175.8913708591563</v>
       </c>
     </row>
     <row r="3">
@@ -531,36 +531,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9522664359394886</v>
+        <v>0.4119346877080224</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03115562352336822</v>
+        <v>0.08993856725494688</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002195839951390111</v>
+        <v>0.02705218711765288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04685979034727013</v>
+        <v>0.1644754909330046</v>
       </c>
       <c r="H3" t="n">
-        <v>195.5243524485682</v>
+        <v>677.0199671156012</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01685715718412651</v>
+        <v>0.1968561246699503</v>
       </c>
       <c r="J3" t="n">
-        <v>-314.3019132733184</v>
+        <v>-181.7193459612371</v>
       </c>
       <c r="K3" t="n">
-        <v>-310.3994258361556</v>
+        <v>-175.8656148054928</v>
       </c>
     </row>
     <row r="4">
@@ -570,36 +570,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9515518307289221</v>
+        <v>0.410685328041638</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03153168303988688</v>
+        <v>0.08986824927223462</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002228713228333022</v>
+        <v>0.02710966017509365</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04720924939387432</v>
+        <v>0.1646501144095978</v>
       </c>
       <c r="H4" t="n">
-        <v>200.4684203320174</v>
+        <v>679.255061126821</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01709455004115648</v>
+        <v>0.1972711637100742</v>
       </c>
       <c r="J4" t="n">
-        <v>-313.5292061608155</v>
+        <v>-181.6089878306328</v>
       </c>
       <c r="K4" t="n">
-        <v>-309.6267187236526</v>
+        <v>-175.7552566748886</v>
       </c>
     </row>
     <row r="5">
@@ -613,38 +613,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9480005860445961</v>
+        <v>0.3032949714818816</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0340522592432233</v>
+        <v>0.09509101985382158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00239207762628829</v>
+        <v>0.03204983256676767</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04890887062985906</v>
+        <v>0.1790246702741487</v>
       </c>
       <c r="H5" t="n">
-        <v>267.0767524443464</v>
+        <v>587.4918354008378</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01827427852502296</v>
+        <v>0.2324463913521729</v>
       </c>
       <c r="J5" t="n">
-        <v>-309.8508355298504</v>
+        <v>-174.9040926272557</v>
       </c>
       <c r="K5" t="n">
-        <v>-305.9483480926876</v>
+        <v>-171.0016051900929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -652,38 +652,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>FS_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8954854271290891</v>
+        <v>0.1468183664654765</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03674135720070883</v>
+        <v>0.1123597533931916</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004807880558038522</v>
+        <v>0.0392480711126541</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06933888200741718</v>
+        <v>0.1981112594292765</v>
       </c>
       <c r="H6" t="n">
-        <v>227.9981707321602</v>
+        <v>1382.283357960172</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03571988825190025</v>
+        <v>0.2844281398392149</v>
       </c>
       <c r="J6" t="n">
-        <v>-273.549944068586</v>
+        <v>-164.3683549385736</v>
       </c>
       <c r="K6" t="n">
-        <v>-269.6474566314232</v>
+        <v>-160.4658675014108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -691,32 +691,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, X_calc</t>
+          <t>T, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7898437461488077</v>
+        <v>0.1261703014281168</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0726232735043195</v>
+        <v>0.09875573739598049</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009667610356015505</v>
+        <v>0.0401979236329993</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09832400701769382</v>
+        <v>0.2004941985020996</v>
       </c>
       <c r="H7" t="n">
-        <v>1426.95857491879</v>
+        <v>1174.847955164787</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07081420340456855</v>
+        <v>0.2912874561146645</v>
       </c>
       <c r="J7" t="n">
-        <v>-237.2266542084102</v>
+        <v>-163.1248766517996</v>
       </c>
       <c r="K7" t="n">
-        <v>-233.3241667712473</v>
+        <v>-159.2223892146368</v>
       </c>
     </row>
     <row r="8">
@@ -726,36 +726,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7417231589653051</v>
+        <v>-0.09869023704055935</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0674211257034051</v>
+        <v>0.09194549874701859</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01188125414946732</v>
+        <v>0.05054196065555808</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1090011658170101</v>
+        <v>0.2248153923901966</v>
       </c>
       <c r="H8" t="n">
-        <v>1097.617392671678</v>
+        <v>580.7581729437879</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08629993021503563</v>
+        <v>0.7319728871421171</v>
       </c>
       <c r="J8" t="n">
-        <v>-228.5052569290943</v>
+        <v>-151.2174719492828</v>
       </c>
       <c r="K8" t="n">
-        <v>-226.5540132105128</v>
+        <v>-147.3149845121199</v>
       </c>
     </row>
     <row r="9">
@@ -769,32 +769,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7400454590884638</v>
+        <v>-0.1772978243428691</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06631542598584311</v>
+        <v>0.09899519332183362</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01195843171809262</v>
+        <v>0.05415806777175795</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1093546145258289</v>
+        <v>0.2327188599399669</v>
       </c>
       <c r="H9" t="n">
-        <v>931.8941862727604</v>
+        <v>638.5184596978429</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08685726447612571</v>
+        <v>0.7831999894861826</v>
       </c>
       <c r="J9" t="n">
-        <v>-228.1685706479828</v>
+        <v>-149.6241130201963</v>
       </c>
       <c r="K9" t="n">
-        <v>-226.2173269294014</v>
+        <v>-147.6728693016149</v>
       </c>
     </row>
     <row r="10">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6880130474590302</v>
+        <v>-0.3017199479029629</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08536575564125881</v>
+        <v>0.1444855613375515</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01435202730375318</v>
+        <v>0.05988173570075868</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1197999470106443</v>
+        <v>0.2447074492138698</v>
       </c>
       <c r="H10" t="n">
-        <v>1494.477364990323</v>
+        <v>1809.84406040135</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1041425048749182</v>
+        <v>0.86586639872284</v>
       </c>
       <c r="J10" t="n">
-        <v>-218.6809317040683</v>
+        <v>-144.3999541436739</v>
       </c>
       <c r="K10" t="n">
-        <v>-216.7296879854869</v>
+        <v>-142.4487104250924</v>
       </c>
     </row>
   </sheetData>
